--- a/sheets/조재수대금교본/검수/상주 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/상주 아리랑.xlsx
@@ -4288,7 +4288,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -4339,17 +4339,9 @@
         </is>
       </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
@@ -4359,17 +4351,9 @@
         </is>
       </c>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N4" s="21"/>
       <c r="O4" s="23"/>
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
@@ -4379,73 +4363,37 @@
         </is>
       </c>
       <c r="S4" s="23"/>
-      <c r="T4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
     <row r="5" ht="106.4" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="24"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="24"/>
       <c r="H5" s="21"/>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="24"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="24"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
-      <c r="R5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R5" s="21"/>
       <c r="S5" s="24"/>
-      <c r="T5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="T5" s="21"/>
       <c r="U5" s="24"/>
     </row>
     <row r="6" ht="106.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋∽
+          <t xml:space="preserve">湳淋
 –</t>
         </is>
       </c>
@@ -4472,7 +4420,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋∽
+          <t xml:space="preserve">湳淋
 –</t>
         </is>
       </c>
@@ -4499,7 +4447,7 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋∽
+          <t xml:space="preserve">湳淋
 –</t>
         </is>
       </c>
@@ -4517,15 +4465,11 @@
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="C7" s="23"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D7" s="21"/>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
@@ -4538,15 +4482,11 @@
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="K7" s="23"/>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L7" s="21"/>
       <c r="M7" s="23"/>
       <c r="N7" s="21"/>
       <c r="O7" s="23"/>
@@ -4555,86 +4495,46 @@
       <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="S7" s="23"/>
-      <c r="T7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="T7" s="21"/>
       <c r="U7" s="23"/>
     </row>
     <row r="8" ht="106.4" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="S8" s="24"/>
-      <c r="T8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="T8" s="21"/>
       <c r="U8" s="24"/>
     </row>
     <row r="9" ht="106.4" customHeight="true">
@@ -4704,11 +4604,7 @@
     </row>
     <row r="10" ht="106.4" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
@@ -4716,23 +4612,11 @@
         </is>
       </c>
       <c r="E10" s="23"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
@@ -4740,19 +4624,11 @@
         </is>
       </c>
       <c r="M10" s="23"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="23"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R10" s="21"/>
       <c r="S10" s="23"/>
       <c r="T10" s="21" t="inlineStr">
         <is>
@@ -4771,9 +4647,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-ﾉ
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -4786,8 +4660,7 @@
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-⊏∼
-‹</t>
+∼</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -4799,9 +4672,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-ﾉ
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -4814,8 +4685,7 @@
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-⊏∼
-‹</t>
+∼</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -4827,20 +4697,14 @@
       <c r="S11" s="24"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-ﾉ
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="U11" s="24"/>
     </row>
     <row r="12" ht="106.4" customHeight="true">
       <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
@@ -4850,7 +4714,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4860,11 +4724,7 @@
         </is>
       </c>
       <c r="I12" s="22"/>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J12" s="21"/>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
@@ -4872,11 +4732,7 @@
         </is>
       </c>
       <c r="M12" s="22"/>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N12" s="21"/>
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
@@ -4884,11 +4740,7 @@
         </is>
       </c>
       <c r="Q12" s="22"/>
-      <c r="R12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="R12" s="21"/>
       <c r="S12" s="22"/>
       <c r="T12" s="21" t="inlineStr">
         <is>
@@ -4933,11 +4785,7 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
@@ -4946,39 +4794,25 @@
         </is>
       </c>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
@@ -4987,11 +4821,7 @@
         </is>
       </c>
       <c r="S14" s="24"/>
-      <c r="T14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T14" s="21"/>
       <c r="U14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/상주 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/상주 아리랑.xlsx
@@ -4288,7 +4288,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -4339,9 +4339,17 @@
         </is>
       </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
@@ -4351,9 +4359,17 @@
         </is>
       </c>
       <c r="K4" s="23"/>
-      <c r="L4" s="21"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O4" s="23"/>
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
@@ -4363,14 +4379,22 @@
         </is>
       </c>
       <c r="S4" s="23"/>
-      <c r="T4" s="21"/>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="U4" s="23"/>
     </row>
     <row r="5" ht="106.4" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="E5" s="24"/>
       <c r="F5" s="21"/>
       <c r="G5" s="24"/>
@@ -4378,7 +4402,11 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21"/>
       <c r="K5" s="24"/>
-      <c r="L5" s="21"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="M5" s="24"/>
       <c r="N5" s="21"/>
       <c r="O5" s="24"/>
@@ -4386,14 +4414,18 @@
       <c r="Q5" s="24"/>
       <c r="R5" s="21"/>
       <c r="S5" s="24"/>
-      <c r="T5" s="21"/>
+      <c r="T5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="U5" s="24"/>
     </row>
     <row r="6" ht="106.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋
+          <t xml:space="preserve">湳淋∽
 –</t>
         </is>
       </c>
@@ -4420,7 +4452,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋
+          <t xml:space="preserve">湳淋∽
 –</t>
         </is>
       </c>
@@ -4447,7 +4479,7 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋
+          <t xml:space="preserve">湳淋∽
 –</t>
         </is>
       </c>
@@ -4465,11 +4497,15 @@
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="C7" s="23"/>
-      <c r="D7" s="21"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
@@ -4482,11 +4518,15 @@
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="K7" s="23"/>
-      <c r="L7" s="21"/>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M7" s="23"/>
       <c r="N7" s="21"/>
       <c r="O7" s="23"/>
@@ -4495,11 +4535,15 @@
       <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="S7" s="23"/>
-      <c r="T7" s="21"/>
+      <c r="T7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="U7" s="23"/>
     </row>
     <row r="8" ht="106.4" customHeight="true">
@@ -4510,11 +4554,20 @@
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21"/>
       <c r="G8" s="24"/>
-      <c r="H8" s="21"/>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+ﾉ</t>
+        </is>
+      </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
@@ -4522,7 +4575,11 @@
         </is>
       </c>
       <c r="K8" s="24"/>
-      <c r="L8" s="21"/>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="M8" s="24"/>
       <c r="N8" s="21"/>
       <c r="O8" s="24"/>
@@ -4534,7 +4591,11 @@
         </is>
       </c>
       <c r="S8" s="24"/>
-      <c r="T8" s="21"/>
+      <c r="T8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="U8" s="24"/>
     </row>
     <row r="9" ht="106.4" customHeight="true">
@@ -4614,7 +4675,11 @@
       <c r="E10" s="23"/>
       <c r="F10" s="21"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="21"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I10" s="23"/>
       <c r="J10" s="21"/>
       <c r="K10" s="23"/>
@@ -4647,7 +4712,8 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞
+ﾉ</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -4660,7 +4726,7 @@
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-∼</t>
+⊏∼</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -4672,7 +4738,8 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞
+ﾉ</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -4685,7 +4752,7 @@
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-∼</t>
+⊏∼</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -4697,14 +4764,19 @@
       <c r="S11" s="24"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞
+ﾉ</t>
         </is>
       </c>
       <c r="U11" s="24"/>
     </row>
     <row r="12" ht="106.4" customHeight="true">
       <c r="A12" s="0"/>
-      <c r="B12" s="21"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
@@ -4714,7 +4786,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">Z∼</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4724,7 +4796,11 @@
         </is>
       </c>
       <c r="I12" s="22"/>
-      <c r="J12" s="21"/>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
@@ -4732,7 +4808,11 @@
         </is>
       </c>
       <c r="M12" s="22"/>
-      <c r="N12" s="21"/>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
@@ -4740,7 +4820,11 @@
         </is>
       </c>
       <c r="Q12" s="22"/>
-      <c r="R12" s="21"/>
+      <c r="R12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="S12" s="22"/>
       <c r="T12" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/상주 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/상주 아리랑.xlsx
@@ -4213,32 +4213,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="106.4" customHeight="true">
+    <row r="3" ht="138.71" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="106.4" customHeight="true">
+    <row r="4" ht="138.71" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="106.4" customHeight="true">
+    <row r="5" ht="138.71" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="106.4" customHeight="true">
+    <row r="6" ht="138.71" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="106.4" customHeight="true">
+    <row r="7" ht="138.71" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="106.4" customHeight="true">
+    <row r="8" ht="138.71" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="106.4" customHeight="true">
+    <row r="9" ht="138.71" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="106.4" customHeight="true">
+    <row r="10" ht="138.71" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="106.4" customHeight="true">
+    <row r="11" ht="138.71" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="106.4" customHeight="true">
+    <row r="12" ht="138.71" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="106.4" customHeight="true">
+    <row r="13" ht="138.71" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4860,7 +4860,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="106.4" customHeight="true">
+    <row r="14" ht="138.71" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4914,6 +4914,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
 </worksheet>
 </file>